--- a/rawresource/excels/equip.xlsx
+++ b/rawresource/excels/equip.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\MServer\rawresource\excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9180" tabRatio="500"/>
   </bookViews>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
   <si>
     <t>equip_weapon_conf</t>
   </si>
@@ -70,7 +75,10 @@
     <t>名字</t>
   </si>
   <si>
-    <t>num</t>
+    <t>int</t>
+  </si>
+  <si>
+    <t>double</t>
   </si>
   <si>
     <t>str</t>
@@ -1376,19 +1384,19 @@
         <v>13</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
@@ -1397,79 +1405,79 @@
         <v>13</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1489,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1504,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1524,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1539,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
